--- a/out/LSTM-mamba2_repeat_4_000006.xlsx
+++ b/out/LSTM-mamba2_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-6.556325642217417e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.08438480768506497</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.1689297339021736</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.0194880177913958</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.06483122663724702</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.06483122663724702</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.06475166442322568</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.2444321660704994</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.5541030433219986</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.0467694028973443</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.4028526571241431</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.08192082715885056</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>-5.684159076306969e-06</v>
+        <v>0.5199482700256048</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0001485803475218452</v>
+        <v>0.04486282609988666</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.0002489201743666781</v>
+        <v>0.527682525776231</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>-0.0001125564142039887</v>
+        <v>0.01852900052948198</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.033977424155455e-05</v>
+        <v>0.5198305874830726</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.02308603502812542</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.480442468088586e-05</v>
+        <v>0.5474763734630048</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002398920802081732</v>
+        <v>0.01389973439154032</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.000511490786917624</v>
+        <v>0.5521757733858368</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0004956931689181736</v>
+        <v>0.01056623891274916</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.00126248838552041</v>
+        <v>0.5594043808195763</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001812936584995618</v>
+        <v>0.004670697256883739</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.001129211008788436</v>
+        <v>0.5581718723189736</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0002321198802615562</v>
+        <v>0.003705173577296268</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.001411409302655957</v>
+        <v>0.5609111095432001</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0001119636107847279</v>
+        <v>0.001836089473792515</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.001402971621154226</v>
+        <v>0.5608732506654687</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>6.821567975456013e-05</v>
+        <v>0.001065585874391671</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.001429266175178112</v>
+        <v>0.561167360520143</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>3.160783987728007e-05</v>
+        <v>0.0005302929371958355</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.001424197354303091</v>
+        <v>0.5611616940443013</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.392175831345849e-05</v>
+        <v>0.0002594676309391166</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.001418469665995915</v>
+        <v>0.5611499993118744</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>6.775902234334416e-06</v>
+        <v>0.0001485320277835259</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.001418084590324433</v>
+        <v>0.5611874566156971</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-2.501004434127891e-06</v>
+        <v>4.633531262135388e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.001407543917941977</v>
+        <v>0.5611314695106868</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.73668118376481e-06</v>
+        <v>1.970370261998147e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.001402582605754025</v>
+        <v>0.5611267567002347</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>-3.536276200927347e-06</v>
+        <v>9.677176780651038e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.001397980831391294</v>
+        <v>0.5611241460540584</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.001397904724379769</v>
+        <v>0.5611186804883393</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.001398444392279955</v>
+        <v>0.5611152958698885</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.001398112288956763</v>
+        <v>0.5611096284396148</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.001398492824014509</v>
+        <v>0.5611100089746726</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.001398721145049203</v>
+        <v>0.5611102372957072</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.001398811089699273</v>
+        <v>0.5611103272403571</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.001397953156114439</v>
+        <v>0.5611094693067723</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.001398181477149017</v>
+        <v>0.561109697627807</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.001397385812937282</v>
+        <v>0.5611089019635953</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.00139744808231038</v>
+        <v>0.5611089642329684</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.001397475757587352</v>
+        <v>0.5611089919082453</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.001397627971610404</v>
+        <v>0.5611091441222685</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.001397282030648785</v>
+        <v>0.5611087981813068</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.001397358137660427</v>
+        <v>0.5611088742883185</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.001397524189322023</v>
+        <v>0.56110904033998</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.001397883967922069</v>
+        <v>0.5611094001185801</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.001397904724379769</v>
+        <v>0.5611094208750378</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.001398008506668266</v>
+        <v>0.5611095246573263</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.00139823682770296</v>
+        <v>0.561109752978361</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.001398112288956763</v>
+        <v>0.5611096284396148</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.001398139964233618</v>
+        <v>0.5611096561148916</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.001398195314787561</v>
+        <v>0.5611097114654455</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.001398458229918382</v>
+        <v>0.5611099743805763</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.001398375204087584</v>
+        <v>0.5611098913547455</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.00139816763951059</v>
+        <v>0.5611096837901687</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.001398181477149017</v>
+        <v>0.561109697627807</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.001398319853533758</v>
+        <v>0.5611098360041917</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.001398036181945237</v>
+        <v>0.5611095523326032</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.00139786321146437</v>
+        <v>0.5611093793621224</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.001397759429175872</v>
+        <v>0.5611092755798339</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.001397904724379769</v>
+        <v>0.5611094208750378</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.00139814688305289</v>
+        <v>0.561109663033711</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.001397973912572139</v>
+        <v>0.5611094900632301</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.001397676403345075</v>
+        <v>0.561109192554003</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.001397662565706647</v>
+        <v>0.5611091787163646</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.001397295868287329</v>
+        <v>0.5611088120189454</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.001397295868287329</v>
+        <v>0.5611088120189454</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.00139723359891423</v>
+        <v>0.5611087497495723</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.001397129816625733</v>
+        <v>0.5611086459672837</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.001396956846144865</v>
+        <v>0.561108472996803</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.001397005277879536</v>
+        <v>0.5611085214285375</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.001396645499279373</v>
+        <v>0.5611081616499375</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.001117822923728731</v>
+        <v>0.5611081201370222</v>
       </c>
     </row>
     <row r="110">
@@ -88383,21 +88383,21 @@
         <v>0</v>
       </c>
       <c r="IY110" t="n">
-        <v>0.0004350694135451623</v>
+        <v>0</v>
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.02729770644840424</v>
+        <v>0.5611081754875759</v>
       </c>
     </row>
     <row r="111">
@@ -89178,21 +89178,21 @@
         <v>0</v>
       </c>
       <c r="IY111" t="n">
-        <v>0.0008125693937117804</v>
+        <v>0</v>
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.05302593878544355</v>
+        <v>0.5611082308381298</v>
       </c>
     </row>
     <row r="112">
@@ -89973,7 +89973,7 @@
         <v>0</v>
       </c>
       <c r="IY112" t="n">
-        <v>0.0343724676532766</v>
+        <v>0</v>
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.0715670390519544</v>
+        <v>0.5611082723510452</v>
       </c>
     </row>
     <row r="113">
@@ -90768,21 +90768,21 @@
         <v>0</v>
       </c>
       <c r="IY113" t="n">
-        <v>-0.02727736318938647</v>
+        <v>0</v>
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.009460476250225794</v>
+        <v>0.561108002517095</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.009175434128574212</v>
+        <v>0.5611080578676491</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.03663431000157834</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.08292743809557938</v>
+        <v>0.5611082031628529</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.073941583477451</v>
+        <v>0.5611081685687567</v>
       </c>
     </row>
     <row r="117">
@@ -93948,21 +93948,21 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.004004826005304556</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.0668832595442168</v>
+        <v>0.5611081547311181</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.02621219466739919</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1024815518071277</v>
+        <v>0.5611082446757683</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.04489471187819023</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1659115354241217</v>
+        <v>0.5611085629414529</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.01346373312669441</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1478087417300949</v>
+        <v>0.5611083830521528</v>
       </c>
     </row>
     <row r="121">
@@ -97128,7 +97128,7 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>0.007768464319085079</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1498294408582812</v>
+        <v>0.5611084245650683</v>
       </c>
     </row>
     <row r="122">
@@ -97923,7 +97923,7 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>0.001551747539340689</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1451333020904569</v>
+        <v>0.561108237756949</v>
       </c>
     </row>
     <row r="123">
@@ -98718,7 +98718,7 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.001205419270601319</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1459831915093963</v>
+        <v>0.5611083069451414</v>
       </c>
     </row>
     <row r="124">
@@ -99513,21 +99513,21 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>-4.751268209849851e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1447150198187858</v>
+        <v>0.5611081062993836</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1443822651987695</v>
+        <v>0.561108147812299</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.01425079848333026</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1596470383818299</v>
+        <v>0.5611081754875759</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_4_000006.xlsx
+++ b/out/LSTM-mamba2_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.331760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-5.34489506308455e-06</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.001105148946217827</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.002212744556460646</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.000261157335081294</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.0008386467160735046</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.0008386467160735046</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.0008114062235553283</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.08368868429874264</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.168355418551862</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.01601288676545557</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.1165703805274572</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.02804787226461888</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC51" t="n">
-        <v>-5.684159076306969e-06</v>
+        <v>0.1566615231646597</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0001485803475218452</v>
+        <v>0.0153602737928722</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.0002489201743666781</v>
+        <v>0.1593095874662593</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>-0.0001125564142039887</v>
+        <v>0.00634143436715735</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.033977424155455e-05</v>
+        <v>0.1566186624580384</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.007901240466024469</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.480442468088586e-05</v>
+        <v>0.1660815426942443</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002398920802081732</v>
+        <v>0.004755551908864373</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.000511490786917624</v>
+        <v>0.1676873159850845</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0004956931689181736</v>
+        <v>0.003615164243574025</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.00126248838552041</v>
+        <v>0.1701592837268484</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001812936584995618</v>
+        <v>0.001595417110021048</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.001129211008788436</v>
+        <v>0.1697339904917826</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0002321198802615562</v>
+        <v>0.00126619475387989</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.001411409302655957</v>
+        <v>0.1706689121808032</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0001119636107847279</v>
+        <v>0.0006253730263528717</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.001402971621154226</v>
+        <v>0.1706526615867973</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>6.821567975456013e-05</v>
+        <v>0.0003615592939493221</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.001429266175178112</v>
+        <v>0.1707500742000828</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>3.160783987728007e-05</v>
+        <v>0.0001782796469746611</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.001424197354303091</v>
+        <v>0.1707448460045499</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.392175831345849e-05</v>
+        <v>8.411409303383277e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.001418469665995915</v>
+        <v>0.1707375555767012</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>6.775902234334416e-06</v>
+        <v>4.840244444644379e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.001418084590324433</v>
+        <v>0.1707473233345523</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-2.501004434127891e-06</v>
+        <v>1.285576091177526e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.001407543917941977</v>
+        <v>0.1707245886893314</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.73668118376481e-06</v>
+        <v>3.983164589084172e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.001402582605754025</v>
+        <v>0.1707196880900257</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>-3.536276200927347e-06</v>
+        <v>-1.076077397829875e-07</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.001397980831391294</v>
+        <v>0.1707154845413002</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.001397904724379769</v>
+        <v>0.1707103293527274</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.001398444392279955</v>
+        <v>0.1707108690206276</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.001398112288956763</v>
+        <v>0.1707105369173044</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.001398492824014509</v>
+        <v>0.1707109174523621</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.001398721145049203</v>
+        <v>0.1707111457733968</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.001398811089699273</v>
+        <v>0.1707112357180468</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.001397953156114439</v>
+        <v>0.1707103777844619</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.001398181477149017</v>
+        <v>0.1707106061054967</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.001397385812937282</v>
+        <v>0.1707098104412849</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.00139744808231038</v>
+        <v>0.170709872710658</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.001397475757587352</v>
+        <v>0.1707099003859349</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.001397627971610404</v>
+        <v>0.1707100525999581</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.001397282030648785</v>
+        <v>0.1707097066589964</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.001397358137660427</v>
+        <v>0.170709782766008</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.001397524189322023</v>
+        <v>0.1707099488176697</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.001397883967922069</v>
+        <v>0.1707103085962697</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.001397904724379769</v>
+        <v>0.1707103293527274</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.001398008506668266</v>
+        <v>0.1707104331350159</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.00139823682770296</v>
+        <v>0.1707106614560506</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.001398112288956763</v>
+        <v>0.1707105369173044</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.001398139964233618</v>
+        <v>0.1707105645925812</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.001398195314787561</v>
+        <v>0.1707106199431352</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.001398458229918382</v>
+        <v>0.1707108828582659</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.001398375204087584</v>
+        <v>0.1707107998324351</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.00139816763951059</v>
+        <v>0.1707105922678583</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.001398181477149017</v>
+        <v>0.1707106061054967</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.001398319853533758</v>
+        <v>0.1707107444818814</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.001398036181945237</v>
+        <v>0.1707104608102928</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.00139786321146437</v>
+        <v>0.170710287839812</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.001397759429175872</v>
+        <v>0.1707101840575235</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.001397904724379769</v>
+        <v>0.1707103293527274</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.00139814688305289</v>
+        <v>0.1707105715114006</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.001397973912572139</v>
+        <v>0.1707103985409197</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.001397676403345075</v>
+        <v>0.1707101010316927</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.001397662565706647</v>
+        <v>0.1707100871940541</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.001397295868287329</v>
+        <v>0.170709720496635</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.001397295868287329</v>
+        <v>0.170709720496635</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.00139723359891423</v>
+        <v>0.1707096582272619</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.001397129816625733</v>
+        <v>0.1707095544449733</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.001396956846144865</v>
+        <v>0.1707093814744926</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.01612649947684261</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.001397005277879536</v>
+        <v>0.1707094299062272</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.001396645499279373</v>
+        <v>0.1707090701276271</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.001117822923728731</v>
+        <v>0.1707090286147117</v>
       </c>
     </row>
     <row r="110">
@@ -88383,21 +88383,21 @@
         <v>0</v>
       </c>
       <c r="IY110" t="n">
-        <v>0.0004350694135451623</v>
+        <v>0</v>
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.02729770644840424</v>
+        <v>0.1707090839652654</v>
       </c>
     </row>
     <row r="111">
@@ -89178,21 +89178,21 @@
         <v>0</v>
       </c>
       <c r="IY111" t="n">
-        <v>0.0008125693937117804</v>
+        <v>0</v>
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.05302593878544355</v>
+        <v>0.1707091393158194</v>
       </c>
     </row>
     <row r="112">
@@ -89973,7 +89973,7 @@
         <v>0</v>
       </c>
       <c r="IY112" t="n">
-        <v>0.0343724676532766</v>
+        <v>0</v>
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.0715670390519544</v>
+        <v>0.1707091808287348</v>
       </c>
     </row>
     <row r="113">
@@ -90768,21 +90768,21 @@
         <v>0</v>
       </c>
       <c r="IY113" t="n">
-        <v>-0.02727736318938647</v>
+        <v>0</v>
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.009460476250225794</v>
+        <v>0.1707089109947847</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.009175434128574212</v>
+        <v>0.1707089663453386</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.03663431000157834</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.08292743809557938</v>
+        <v>0.1707091116405425</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.073941583477451</v>
+        <v>0.1707090770464463</v>
       </c>
     </row>
     <row r="117">
@@ -93948,21 +93948,21 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.004004826005304556</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.331760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.0668832595442168</v>
+        <v>0.1707090632088077</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.02621219466739919</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1024815518071277</v>
+        <v>0.1707091531534579</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.04489471187819023</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1659115354241217</v>
+        <v>0.1707094714191426</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.01346373312669441</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1478087417300949</v>
+        <v>0.1707092915298424</v>
       </c>
     </row>
     <row r="121">
@@ -97128,7 +97128,7 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>0.007768464319085079</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1498294408582812</v>
+        <v>0.1707093330427578</v>
       </c>
     </row>
     <row r="122">
@@ -97923,7 +97923,7 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>0.001551747539340689</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1451333020904569</v>
+        <v>0.1707091462346385</v>
       </c>
     </row>
     <row r="123">
@@ -98718,7 +98718,7 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.001205419270601319</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1459831915093963</v>
+        <v>0.170709215422831</v>
       </c>
     </row>
     <row r="124">
@@ -99513,21 +99513,21 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>-4.751268209849851e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1447150198187858</v>
+        <v>0.1707090147770732</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586083</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1443822651987695</v>
+        <v>0.1707090562899886</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.01425079848333026</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1596470383818299</v>
+        <v>0.1707090839652654</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_4_000006.xlsx
+++ b/out/LSTM-mamba2_repeat_4_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.2308091819286346</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.08417461812496185</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01720745116472244</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.4313973956586084</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.0536089800298214</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.0561593659222126</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.04937175288796425</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.038533765822649</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.02856289222836494</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.02338749170303345</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.278921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.02119279094040394</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.278921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.02234675921499729</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.02006258815526962</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01696059107780457</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01356848701834679</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01444484479725361</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.01647517271339893</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01776910573244095</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01664776355028152</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.078921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01597832702100277</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.078921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01667264476418495</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.078921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01858269050717354</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.078921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.02109206467866898</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.078921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.02024505473673344</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.078921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01803626865148544</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.078921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.01585233584046364</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01772991195321083</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.005812468007206917</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.00763714499771595</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01079969853162766</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01276696845889091</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01137579791247845</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01144803501665592</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01108445785939693</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.005416864529252052</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.00618104450404644</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.009197894483804703</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01054226420819759</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.009714357554912567</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.009585097432136536</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.00814400240778923</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.005613263696432114</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4313973956586084</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.001418879255652428</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.02117135189473629</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-5.34489506308455e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.001105148946217827</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.03499037027359009</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.002212744556460646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.000261157335081294</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.03386645019054413</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.0008386467160735046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.02517267689108849</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.0008386467160735046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.02818771824240685</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.0008114062235553283</v>
+        <v>-1.572706125420518e-05</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.08368868429874264</v>
+        <v>0.0483169334537267</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0374429002404213</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.168355418551862</v>
+        <v>0.09671435015372233</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01601288676545557</v>
+        <v>0.00924483870115754</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.04110768809914589</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.1165703805274572</v>
+        <v>0.06681670935983816</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.02804787226461888</v>
+        <v>0.01619342928458149</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.04788943007588387</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.1566615231646597</v>
+        <v>0.08996313684407575</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0153602737928722</v>
+        <v>0.008866366249509762</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.05174227803945541</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1593095874662593</v>
+        <v>0.09149022721617087</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00634143436715735</v>
+        <v>0.003659054835664152</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.04538416862487793</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1566186624580384</v>
+        <v>0.08993453340209276</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.007901240466024469</v>
+        <v>0.004559387025061533</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.05889410898089409</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1660815426942443</v>
+        <v>0.09539572624475672</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.004755551908864373</v>
+        <v>0.002743335502610705</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.06159806996583939</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1676873159850845</v>
+        <v>0.09632073378365487</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.003615164243574025</v>
+        <v>0.002084454598152154</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.06725084781646729</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1701592837268484</v>
+        <v>0.09774598404177814</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.001595417110021048</v>
+        <v>0.0009199679821571501</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.07154077291488647</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.1697339904917826</v>
+        <v>0.09749819371384895</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.00126619475387989</v>
+        <v>0.0007289636376568415</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.07335448265075684</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.1706689121808032</v>
+        <v>0.09803588659381936</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0006253730263528717</v>
+        <v>0.0003577146381792318</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.06254415959119797</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1706526615867973</v>
+        <v>0.09802439228128665</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0003615592939493221</v>
+        <v>0.0002073716544309565</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01050414517521858</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.1707500742000828</v>
+        <v>0.09807872657311079</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0001782796469746611</v>
+        <v>9.973122684266348e-05</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.02928730472922325</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1707448460045499</v>
+        <v>0.0980735961756634</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>8.411409303383277e-05</v>
+        <v>4.674366692287064e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.0567147471010685</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1707375555767012</v>
+        <v>0.0980672517426142</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>4.840244444644379e-05</v>
+        <v>2.503887500112463e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.06256280094385147</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1707473233345523</v>
+        <v>0.09807102216729405</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>1.285576091177526e-05</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.09431619942188263</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1707245886893314</v>
+        <v>0.09805493801403116</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>3.983164589084172e-06</v>
+        <v>-5.08417705457914e-07</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.1093267649412155</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1707196880900257</v>
+        <v>0.09805000155201671</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>-1.076077397829875e-07</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.1169057488441467</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1707154845413002</v>
+        <v>0.09804560042341171</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.1061502248048782</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1707103293527274</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.09374560415744781</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1707108690206276</v>
+        <v>0.09804098490273906</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.08268645405769348</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1707105369173044</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.06515343487262726</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1707109174523621</v>
+        <v>0.09804103333447362</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.0677611380815506</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1707111457733968</v>
+        <v>0.0980412616555083</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.07081568241119385</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1707112357180468</v>
+        <v>0.09804135160015826</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.06915967166423798</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1707103777844619</v>
+        <v>0.09804049366657343</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.06514668464660645</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1707106061054967</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.06543448567390442</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1707098104412849</v>
+        <v>0.09803992632339639</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.06201675161719322</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.170709872710658</v>
+        <v>0.09803998859276948</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.05797908082604408</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1707099003859349</v>
+        <v>0.09804001626804634</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.055098757147789</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1707100525999581</v>
+        <v>0.09804016848206963</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.05287887528538704</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1707097066589964</v>
+        <v>0.09803982254110789</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.04698606207966805</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.170709782766008</v>
+        <v>0.09803989864811953</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.04429074749350548</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1707099488176697</v>
+        <v>0.09804006469978113</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.04251273348927498</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1707103085962697</v>
+        <v>0.09804042447838117</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.03985268995165825</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1707103293527274</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.02961386367678642</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1707104331350159</v>
+        <v>0.09804054901712737</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.03170695900917053</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1707106614560506</v>
+        <v>0.09804077733816206</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.0380951501429081</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1707105369173044</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.04310010001063347</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1707105645925812</v>
+        <v>0.09804068047469272</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.0424247607588768</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.16</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1707106199431352</v>
+        <v>0.09804073582524667</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.04371416196227074</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1707108828582659</v>
+        <v>0.09804099874037737</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.04173991084098816</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1707107998324351</v>
+        <v>0.09804091571454657</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.03692489489912987</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1707105922678583</v>
+        <v>0.0980407081499698</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.03478889167308807</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1707106061054967</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.03371563926339149</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1707107444818814</v>
+        <v>0.09804086036399286</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.03410613164305687</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1707104608102928</v>
+        <v>0.09804057669240422</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.02759692072868347</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.170710287839812</v>
+        <v>0.09804040372192348</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.02151781320571899</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1707101840575235</v>
+        <v>0.09804029993963498</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01691862568259239</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1707103293527274</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01706072315573692</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1707105715114006</v>
+        <v>0.09804068739351211</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01955771073698997</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1707103985409197</v>
+        <v>0.09804051442303113</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01374604552984238</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1707101010316927</v>
+        <v>0.09804021691380418</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01486047357320786</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1707100871940541</v>
+        <v>0.09804020307616564</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.007677711546421051</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.170709720496635</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.003419402986764908</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.170709720496635</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01691957376897335</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1707096582272619</v>
+        <v>0.09803977410937334</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.008133634924888611</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1707095544449733</v>
+        <v>0.09803967032708484</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.002177061513066292</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1707093814744926</v>
+        <v>0.09803949735660408</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.002489851787686348</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.01612649947684261</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1707094299062272</v>
+        <v>0.09803954578833864</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.0003827512264251709</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.6313973956586084</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1707090701276271</v>
+        <v>0.0980391860097386</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.005895894020795822</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.278921290794059</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1707090286147117</v>
+        <v>0.09803914449682319</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.002575758844614029</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.278921290794059</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1707090839652654</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.005824830383062363</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.278921290794059</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1707091393158194</v>
+        <v>0.09803925519793084</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.007040981203317642</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.278921290794059</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1707091808287348</v>
+        <v>0.09803929671084624</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.009675048291683197</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.278921290794059</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1707089109947847</v>
+        <v>0.09803902687689615</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.01299294829368591</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.278921290794059</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1707089663453386</v>
+        <v>0.0980390822274501</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.01223691925406456</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.278921290794059</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1707091116405425</v>
+        <v>0.098039227522654</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.01339395716786385</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.278921290794059</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1707090770464463</v>
+        <v>0.09803919292855776</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01230765506625175</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.278921290794059</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1707090632088077</v>
+        <v>0.09803917909091921</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.009587768465280533</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.4313973956586084</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1707091531534579</v>
+        <v>0.09803926903556939</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.004192888736724854</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1707094714191426</v>
+        <v>0.09803958730125403</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.004607310518622398</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1707092915298424</v>
+        <v>0.0980394074119539</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.001873232424259186</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1707093330427578</v>
+        <v>0.09803944892486929</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.0009442958980798721</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1707091462346385</v>
+        <v>0.09803926211675</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.0003938209265470505</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.170709215422831</v>
+        <v>0.0980393313049425</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.001252710819244385</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.4313973956586084</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1707090147770732</v>
+        <v>0.09803913065918465</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.001221077516674995</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.6313973956586083</v>
+        <v>-0.08999999999999997</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1707090562899886</v>
+        <v>0.09803917217210005</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>2.799183130264282e-05</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.278921290794059</v>
+        <v>0.58</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1707090839652654</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
   </sheetData>
